--- a/templates/05. Template_Planilha Seguro de Vida.xlsx
+++ b/templates/05. Template_Planilha Seguro de Vida.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulo.rodrigues\Documents\Rodrigues\06. Projetos\bdSter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulo.rodrigues\Documents\Rodrigues\11. Automação Google Sheets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD85A71-2C63-47D5-A25C-5C4B1A4C84CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18507258-48D9-459F-A2EB-40A0E9EA3260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,7 +94,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -215,10 +215,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -243,7 +243,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="22" formatCode="mmm/yy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -262,10 +262,188 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="22" formatCode="mmm/yy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -292,184 +470,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -484,18 +484,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5AC6B599-0524-4B4C-8FF8-8BD41F5F10E5}" name="tb_Seguro" displayName="tb_Seguro" ref="A1:I4" totalsRowShown="0" headerRowDxfId="3" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5AC6B599-0524-4B4C-8FF8-8BD41F5F10E5}" name="tb_Seguro" displayName="tb_Seguro" ref="A1:I4" totalsRowShown="0" headerRowDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="A1:I4" xr:uid="{5AC6B599-0524-4B4C-8FF8-8BD41F5F10E5}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{24919905-C26D-472C-90D9-C7022AA653F0}" name="Substipulamento " dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{45DB8087-CCF4-421F-AB9C-34A1A7A30BE0}" name="Modulo" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{0F4A3731-25CA-40F9-88F2-8E124F173039}" name="Vigência " dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{24919905-C26D-472C-90D9-C7022AA653F0}" name="Substipulamento " dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{45DB8087-CCF4-421F-AB9C-34A1A7A30BE0}" name="Modulo" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{0F4A3731-25CA-40F9-88F2-8E124F173039}" name="Vigência " dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{FA341A86-02BD-4D5F-9FA9-1882B9C6275F}" name="Nome "/>
-    <tableColumn id="5" xr3:uid="{B7C183B5-9BB0-4C71-A565-4F141A563573}" name="Cargo/Profissão " dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{8A70D701-24A9-4194-B600-36B1F89DE97B}" name="Data de Nascimento " dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{2B15F63F-D80D-4784-B860-2371D1B4E8FB}" name="Data de Admissão " dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{4B887F85-4AC1-4320-84F5-337A69632770}" name="CPF " dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{A0666283-D336-4629-8290-DB60C960D682}" name="SEXO" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{B7C183B5-9BB0-4C71-A565-4F141A563573}" name="Cargo/Profissão " dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{8A70D701-24A9-4194-B600-36B1F89DE97B}" name="Data de Nascimento " dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{2B15F63F-D80D-4784-B860-2371D1B4E8FB}" name="Data de Admissão " dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{4B887F85-4AC1-4320-84F5-337A69632770}" name="CPF " dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{A0666283-D336-4629-8290-DB60C960D682}" name="SEXO" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
